--- a/Printers.xlsx
+++ b/Printers.xlsx
@@ -474,6 +474,16 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EALAN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -489,6 +499,16 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EALAN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -504,6 +524,16 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EALAN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -519,6 +549,16 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EALAN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -534,6 +574,16 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>iANAN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -549,6 +599,16 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>iANAN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -559,6 +619,11 @@
           <t>heavy</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>iANAN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -569,6 +634,11 @@
           <t>heavy</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>iANAN</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -584,6 +654,11 @@
           <t>t</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>iANAN</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -619,6 +694,11 @@
       <c r="A13" s="1" t="n">
         <v>0.7083333333333334</v>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -629,6 +709,11 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -639,6 +724,11 @@
           <t>bol</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -647,6 +737,11 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>bol</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alan</t>
         </is>
       </c>
     </row>

--- a/Printers.xlsx
+++ b/Printers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FDM" sheetId="1" state="visible" r:id="rId1"/>
@@ -469,11 +469,6 @@
           <t>g</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -499,11 +494,6 @@
           <t>g</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -529,11 +519,6 @@
           <t>g</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -559,11 +544,6 @@
           <t>heavy</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>EALAN</t>
@@ -591,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bol</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -616,7 +596,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bol</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -641,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bunny</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -666,7 +646,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bunny</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -691,7 +671,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -716,7 +696,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -741,7 +721,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -761,7 +741,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -786,7 +766,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Bardock</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -806,7 +786,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Bardock</t>
         </is>
       </c>
     </row>
@@ -821,13 +801,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Bardock</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>0.875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -993,6 +978,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -1003,6 +993,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1013,6 +1008,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1023,6 +1023,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1033,6 +1038,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1043,6 +1053,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1053,6 +1068,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1063,6 +1083,11 @@
           <t>e</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1073,6 +1098,11 @@
           <t>t</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1081,6 +1111,11 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>t</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bardock</t>
         </is>
       </c>
     </row>

--- a/Printers.xlsx
+++ b/Printers.xlsx
@@ -467,410 +467,80 @@
       <c r="A2" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ejlf</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EALAN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Falan</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sinclair</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ejlf</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EALAN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Falan</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sinclair</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ejlf</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EALAN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Falan</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sinclair</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>0.375</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EALAN</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Falan</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sinclair</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>iANAN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Falan</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>iANAN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Falan</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>iANAN</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>body of a calculater</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>iANAN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>body of a calculater</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>iANAN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>body of a calculater</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>0.625</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sisko</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>body of a calculater</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sisko</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>body of a calculater</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sisko</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>body of a calculater</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Alfred</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sisko</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>0.875</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bardock</t>
-        </is>
       </c>
     </row>
     <row r="18">
